--- a/Vegetation/Ergebnisse_species_richness.xlsx
+++ b/Vegetation/Ergebnisse_species_richness.xlsx
@@ -379,5560 +379,5560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1.156027655202271</v>
+        <v>1.020592004227205</v>
       </c>
       <c r="D2">
-        <v>0.4652197519375215</v>
+        <v>0.7362015116347587</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0.836386862720723</v>
+        <v>1.039635030233855</v>
       </c>
       <c r="D3">
-        <v>0.6033255895559327</v>
+        <v>0.6459615634762322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>0.9266767387691077</v>
+        <v>1.476352099299954</v>
       </c>
       <c r="D4">
-        <v>0.575776630841018</v>
+        <v>0.758694896584348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0.19451688279324</v>
+        <v>1.206337125031212</v>
       </c>
       <c r="D5">
-        <v>0.2806285421749871</v>
+        <v>0.6732695686832003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>0.662192181868297</v>
+        <v>1.219152983197208</v>
       </c>
       <c r="D6">
-        <v>0.9553413768968346</v>
+        <v>0.5862886543145326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L103</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0.662192181868297</v>
+        <v>1.240240595784448</v>
       </c>
       <c r="D7">
-        <v>0.9553413768968346</v>
+        <v>0.7706048094199043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L104</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0.662192181868297</v>
+        <v>1.506428853865558</v>
       </c>
       <c r="D8">
-        <v>0.9553413768968346</v>
+        <v>0.7244391456412952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L105</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0.6693692425153493</v>
+        <v>0.9734863771041283</v>
       </c>
       <c r="D9">
-        <v>0.6092861416349635</v>
+        <v>0.6048610944126672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L106</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0.662192181868297</v>
+        <v>0.7934541620946818</v>
       </c>
       <c r="D10">
-        <v>0.9553413768968346</v>
+        <v>0.4930007898811508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L107</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.755017152900669</v>
+        <v>0.640185309289103</v>
       </c>
       <c r="D11">
-        <v>0.4213830962623312</v>
+        <v>0.4617960854806781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L108</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>0.662192181868297</v>
+        <v>0.4281198529765204</v>
       </c>
       <c r="D12">
-        <v>0.9553413768968346</v>
+        <v>0.266005820832837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L109</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>0.4555869118836413</v>
+        <v>0.9023690239276578</v>
       </c>
       <c r="D13">
-        <v>0.6572729784684465</v>
+        <v>0.5036217413247025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>1.068652425547084</v>
+        <v>0.4767868677720328</v>
       </c>
       <c r="D14">
-        <v>0.5964262747875932</v>
+        <v>0.2962443372860183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.03423054971755033</v>
+      </c>
+      <c r="D15">
+        <v>0.04938424432441297</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L111</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1.09861228866811</v>
+        <v>0.06811529608647736</v>
       </c>
       <c r="D16">
-        <v>0.9999999999999998</v>
+        <v>0.06200121443121319</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L112</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>1.121900162570469</v>
+        <v>0.8676768615147434</v>
       </c>
       <c r="D17">
-        <v>0.8092799004564688</v>
+        <v>0.5391179459681525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L113</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>0.19451688279324</v>
+        <v>1.030966024605707</v>
       </c>
       <c r="D18">
-        <v>0.2806285421749871</v>
+        <v>0.7436847855118315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L114</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>0.19451688279324</v>
+        <v>0.9021241814080119</v>
       </c>
       <c r="D19">
-        <v>0.2806285421749871</v>
+        <v>0.6507450413916772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L115</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.708018976056273</v>
+      </c>
+      <c r="D20">
+        <v>0.6444666452025871</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L116</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>0.19451688279324</v>
+        <v>0.08671091094332455</v>
       </c>
       <c r="D21">
-        <v>0.2806285421749871</v>
+        <v>0.05387651817657488</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L117</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>0.19451688279324</v>
+        <v>0.3682207759404497</v>
       </c>
       <c r="D22">
-        <v>0.2806285421749871</v>
+        <v>0.2287884317224488</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L118</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>0.19451688279324</v>
+        <v>1.364827789086023</v>
       </c>
       <c r="D23">
-        <v>0.2806285421749871</v>
+        <v>0.6563434276606179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L119</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>0.19451688279324</v>
+        <v>0.7290149744224851</v>
       </c>
       <c r="D24">
-        <v>0.2806285421749871</v>
+        <v>0.4529624714257719</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>0.607271814155035</v>
+        <v>0.773826687226959</v>
       </c>
       <c r="D25">
-        <v>0.5527626264687555</v>
+        <v>0.4318808972503141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L120</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>0.19451688279324</v>
+        <v>1.359443731813305</v>
       </c>
       <c r="D26">
-        <v>0.2806285421749871</v>
+        <v>0.6537542434182135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L121</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>0.8102359754965719</v>
+        <v>1.509153859937444</v>
       </c>
       <c r="D27">
-        <v>0.7375085677212407</v>
+        <v>0.6868455211651825</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L122</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.9485670767867524</v>
+        <v>0.9079997485322008</v>
       </c>
       <c r="D28">
-        <v>0.5294053655513394</v>
+        <v>0.5067643085616815</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L123</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29">
-        <v>0.4127157986058386</v>
+        <v>0.7173630342061832</v>
       </c>
       <c r="D29">
-        <v>0.2977115179725858</v>
+        <v>0.5174680459831602</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L124</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>0.00883143005016138</v>
+        <v>0.9416329786242219</v>
       </c>
       <c r="D30">
-        <v>0.01274106033732559</v>
+        <v>0.4528297428662228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L125</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>1.247010772072043</v>
+        <v>0.7347804129124217</v>
       </c>
       <c r="D31">
-        <v>0.7748113564605138</v>
+        <v>0.3776024362014544</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L126</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>0.2771070250309874</v>
+        <v>0.7926128795467399</v>
       </c>
       <c r="D32">
-        <v>0.1721762752636373</v>
+        <v>0.5717493353334014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L127</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
       <c r="C33">
-        <v>0.6446717045884102</v>
+        <v>0.9739004879384758</v>
       </c>
       <c r="D33">
-        <v>0.4005570513828732</v>
+        <v>0.6051183959408269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L128</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>1.39837008467158</v>
+        <v>0.7278048664104161</v>
       </c>
       <c r="D34">
-        <v>0.7186200685321729</v>
+        <v>0.6624765387366658</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L129</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>0.20276290568803</v>
+        <v>0.1649791295575473</v>
       </c>
       <c r="D35">
-        <v>0.1845627504620828</v>
+        <v>0.1190072860314256</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36">
-        <v>0.607271814155035</v>
+        <v>0.6211056731868858</v>
       </c>
       <c r="D36">
-        <v>0.5527626264687555</v>
+        <v>0.5653547476151721</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>0.8102359754965719</v>
+        <v>0.7728200659624421</v>
       </c>
       <c r="D37">
-        <v>0.7375085677212407</v>
+        <v>0.5574718383317484</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>0.8170082613435337</v>
+        <v>1.019056018424425</v>
       </c>
       <c r="D38">
-        <v>0.5893468835028152</v>
+        <v>0.7350935320844851</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>0.8102359754965719</v>
+        <v>0.5004024235381879</v>
       </c>
       <c r="D39">
-        <v>0.7375085677212407</v>
+        <v>0.7219280948873623</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>1.430458048303307</v>
+        <v>0.9887339357979354</v>
       </c>
       <c r="D40">
-        <v>0.6510295138048688</v>
+        <v>0.4754805153114361</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>1.02998864247627</v>
+        <v>0.8674284029982893</v>
       </c>
       <c r="D41">
-        <v>0.9375360653620259</v>
+        <v>0.4841210094857231</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>0.8699354897077656</v>
+        <v>0.9477353118178559</v>
       </c>
       <c r="D42">
-        <v>0.7918494073668355</v>
+        <v>0.4870396057484749</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0.9683146857576469</v>
+        <v>0.8568847365088091</v>
       </c>
       <c r="D43">
-        <v>0.3775180523314358</v>
+        <v>0.6181116799873525</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44">
-        <v>0.8699354897077656</v>
+        <v>0.3972454932559829</v>
       </c>
       <c r="D44">
-        <v>0.7918494073668355</v>
+        <v>0.3615884305623224</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0.6900175350139677</v>
+        <v>0.502262918546141</v>
       </c>
       <c r="D45">
-        <v>0.6280810274300705</v>
+        <v>0.3623061109044675</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46">
-        <v>0.6931471805599453</v>
+        <v>0.0118011300326326</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0.01702543177496486</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>0.8699354897077656</v>
+        <v>0.0576346077189195</v>
       </c>
       <c r="D47">
-        <v>0.7918494073668355</v>
+        <v>0.05246128075701044</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>0.8699354897077656</v>
+        <v>0.2664108619040347</v>
       </c>
       <c r="D48">
-        <v>0.7918494073668355</v>
+        <v>0.1921748146539526</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>0.8699354897077656</v>
+        <v>0.4706255754642422</v>
       </c>
       <c r="D49">
-        <v>0.7918494073668355</v>
+        <v>0.2924161111331546</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50">
-        <v>0.662192181868297</v>
+        <v>0.08082938714559725</v>
       </c>
       <c r="D50">
-        <v>0.9553413768968346</v>
+        <v>0.05022212197260319</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L27</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C51">
-        <v>0.4555869118836413</v>
+        <v>0.5485892608214828</v>
       </c>
       <c r="D51">
-        <v>0.6572729784684465</v>
+        <v>0.3061734960763634</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L28</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>0.4555869118836413</v>
+        <v>0.3682207759404497</v>
       </c>
       <c r="D52">
-        <v>0.6572729784684465</v>
+        <v>0.2287884317224488</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C53">
-        <v>0.5216705256352127</v>
+        <v>0.4857472289679715</v>
       </c>
       <c r="D53">
-        <v>0.2508704934372867</v>
+        <v>0.2711006903048467</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>0.19451688279324</v>
+        <v>0.4281198529765204</v>
       </c>
       <c r="D54">
-        <v>0.2806285421749871</v>
+        <v>0.266005820832837</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L31</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>0.4555869118836413</v>
+        <v>1.285293024120099</v>
       </c>
       <c r="D55">
-        <v>0.6572729784684465</v>
+        <v>0.9271429359936232</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L32</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>0.4555869118836413</v>
+        <v>0.862314347241475</v>
       </c>
       <c r="D56">
-        <v>0.6572729784684465</v>
+        <v>0.5357860285130963</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L33</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
       <c r="C57">
-        <v>0.5380247029595945</v>
+        <v>0.511172191333868</v>
       </c>
       <c r="D57">
-        <v>0.3342935436048542</v>
+        <v>0.3176091400511223</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L34</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>0.19451688279324</v>
+        <v>0.4434581029780121</v>
       </c>
       <c r="D58">
-        <v>0.2806285421749871</v>
+        <v>0.2474986797022859</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L35</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C59">
-        <v>0.20276290568803</v>
+        <v>0.4410441397088374</v>
       </c>
       <c r="D59">
-        <v>0.1845627504620828</v>
+        <v>0.2461514211496551</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L36</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60">
         <v>4</v>
       </c>
       <c r="C60">
-        <v>0.2351010815977794</v>
+        <v>1.039130927084559</v>
       </c>
       <c r="D60">
-        <v>0.169589582264374</v>
+        <v>0.749574517669622</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L37</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C61">
-        <v>0.4555869118836413</v>
+        <v>0.7406479077512897</v>
       </c>
       <c r="D61">
-        <v>0.6572729784684465</v>
+        <v>0.4133634678489427</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L38</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>0.4833021896008116</v>
+        <v>0.2752067937223205</v>
       </c>
       <c r="D62">
-        <v>0.4399206112892998</v>
+        <v>0.1535958360755242</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L39</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>0.4833021896008116</v>
+        <v>0.6349755035427602</v>
       </c>
       <c r="D63">
-        <v>0.4399206112892998</v>
+        <v>0.4580380050235563</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C64">
-        <v>0.4034855815444305</v>
+        <v>0.4396636161300515</v>
       </c>
       <c r="D64">
-        <v>0.2910533237821747</v>
+        <v>0.2259424035295239</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C65">
-        <v>0.4555869118836413</v>
+        <v>0.3534440494092194</v>
       </c>
       <c r="D65">
-        <v>0.6572729784684465</v>
+        <v>0.1816343111118501</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L41</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>0.662192181868297</v>
+        <v>0.8788267410129095</v>
       </c>
       <c r="D66">
-        <v>0.9553413768968346</v>
+        <v>0.546045755616493</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L42</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>0.6931471805599453</v>
+        <v>1.173252423569263</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0.564215151064778</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C68">
-        <v>0.662192181868297</v>
+        <v>1.49181149092682</v>
       </c>
       <c r="D68">
-        <v>0.9553413768968346</v>
+        <v>0.7666394523154394</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L44</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C69">
-        <v>0.6931471805599453</v>
+        <v>1.704568598372718</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0.7402847362988317</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L45</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>0.662192181868297</v>
+        <v>0.8369882167858358</v>
       </c>
       <c r="D70">
-        <v>0.9553413768968346</v>
+        <v>0.603759374819711</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L46</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4626659965444074</v>
+        <v>0.2846002445573275</v>
       </c>
       <c r="D71">
-        <v>0.4211367388811164</v>
+        <v>0.1588384208065282</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L47</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>0.20276290568803</v>
+        <v>0.3972454932559829</v>
       </c>
       <c r="D72">
-        <v>0.1845627504620828</v>
+        <v>0.3615884305623224</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L48</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C73">
-        <v>0.2590219627222835</v>
+        <v>0.6474509497201001</v>
       </c>
       <c r="D73">
-        <v>0.1868448505503822</v>
+        <v>0.4022838934748969</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L49</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C74">
-        <v>0.607271814155035</v>
+        <v>1.167927660369051</v>
       </c>
       <c r="D74">
-        <v>0.5527626264687555</v>
+        <v>0.6518328382951034</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C75">
-        <v>1.213630920484374</v>
+        <v>1.146046065801054</v>
       </c>
       <c r="D75">
-        <v>0.6236829182855944</v>
+        <v>0.5511316585871623</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C76">
-        <v>0.8102359754965719</v>
+        <v>1.456984643522396</v>
       </c>
       <c r="D76">
-        <v>0.7375085677212407</v>
+        <v>0.7006615066203783</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L51</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C77">
-        <v>1.048792231404724</v>
+        <v>1.098136135936212</v>
       </c>
       <c r="D77">
-        <v>0.9546518296060714</v>
+        <v>0.5643303399539427</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L52</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C78">
-        <v>0.19451688279324</v>
+        <v>1.470647910959634</v>
       </c>
       <c r="D78">
-        <v>0.2806285421749871</v>
+        <v>0.8207842270219642</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L53</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C79">
-        <v>0.662192181868297</v>
+        <v>1.048585831905833</v>
       </c>
       <c r="D79">
-        <v>0.9553413768968346</v>
+        <v>0.5852268956377251</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L54</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>0.8102359754965719</v>
+        <v>0.6790268485207671</v>
       </c>
       <c r="D80">
-        <v>0.7375085677212407</v>
+        <v>0.489814333495686</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L55</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C81">
-        <v>0.5638225808048839</v>
+        <v>0.966329936545508</v>
       </c>
       <c r="D81">
-        <v>0.513213429906585</v>
+        <v>0.496595352573003</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L56</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C82">
-        <v>0.2269283709027674</v>
+        <v>0.6947669929073684</v>
       </c>
       <c r="D82">
-        <v>0.2065591048302231</v>
+        <v>0.4316830040722781</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L57</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>0.5975603177003802</v>
+        <v>1.240924692823335</v>
       </c>
       <c r="D83">
-        <v>0.431048653489186</v>
+        <v>0.6925732578145454</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L58</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C84">
-        <v>0.662192181868297</v>
+        <v>1.312868226895126</v>
       </c>
       <c r="D84">
-        <v>0.9553413768968346</v>
+        <v>0.6746808055513193</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L59</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C85">
-        <v>0.6931471805599453</v>
+        <v>0.6446717045884102</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0.4005570513828732</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C86">
-        <v>0.5081267731378364</v>
+        <v>0.615988059031729</v>
       </c>
       <c r="D86">
-        <v>0.2044852562896828</v>
+        <v>0.2803482472322038</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L60</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C87">
-        <v>0.7280100277746424</v>
+        <v>1.240931968485071</v>
       </c>
       <c r="D87">
-        <v>0.6626632846581728</v>
+        <v>0.771034383431602</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L61</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C88">
-        <v>0.6931471805599453</v>
+        <v>1.646112134736446</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0.7491779182317774</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L62</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C89">
-        <v>0.662192181868297</v>
+        <v>1.08431193273859</v>
       </c>
       <c r="D89">
-        <v>0.9553413768968346</v>
+        <v>0.5572261048461018</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L63</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>1.365304352400869</v>
+        <v>1.723836118994475</v>
       </c>
       <c r="D90">
-        <v>0.7619908675515937</v>
+        <v>0.9620912564436768</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L64</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91">
-        <v>1.218987605137656</v>
+        <v>1.229398558534492</v>
       </c>
       <c r="D91">
-        <v>0.6803299360615819</v>
+        <v>0.5126990208791605</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L65</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C92">
-        <v>1.245446142364597</v>
+        <v>0.4127157986058386</v>
       </c>
       <c r="D92">
-        <v>0.695096726850939</v>
+        <v>0.2977115179725858</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L66</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>1.213579666667576</v>
+        <v>0.103483417174611</v>
       </c>
       <c r="D93">
-        <v>0.7540394427717741</v>
+        <v>0.0746475063860275</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>L67</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94">
         <v>5</v>
       </c>
       <c r="C94">
-        <v>1.228890586157654</v>
+        <v>1.231325910644499</v>
       </c>
       <c r="D94">
-        <v>0.763552651931189</v>
+        <v>0.7650658041118541</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>L68</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C95">
-        <v>1.715612302311079</v>
+        <v>0.7870187704033657</v>
       </c>
       <c r="D95">
-        <v>0.6688679046704358</v>
+        <v>0.404447641524169</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L69</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C96">
-        <v>1.096342189139819</v>
+        <v>1.402665586529982</v>
       </c>
       <c r="D96">
-        <v>0.4761353630211544</v>
+        <v>0.7208275198168519</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C97">
-        <v>1.184605387662923</v>
+        <v>1.096307977892248</v>
       </c>
       <c r="D97">
-        <v>0.5391371459621421</v>
+        <v>0.6811744457008606</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L70</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C98">
-        <v>1.515376040227951</v>
+        <v>0.9654366173391478</v>
       </c>
       <c r="D98">
-        <v>0.6581194522793991</v>
+        <v>0.5388204353986685</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L71</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C99">
-        <v>0.19451688279324</v>
+        <v>1.549290658738799</v>
       </c>
       <c r="D99">
-        <v>0.2806285421749871</v>
+        <v>0.7450513167526869</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L72</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C100">
-        <v>1.25279924147191</v>
+        <v>1.63956968219039</v>
       </c>
       <c r="D100">
-        <v>0.7784079347162806</v>
+        <v>0.7462003197588951</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L73</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C101">
-        <v>0.2351010815977794</v>
+        <v>1.106494586142389</v>
       </c>
       <c r="D101">
-        <v>0.169589582264374</v>
+        <v>0.6175463867474918</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L74</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102">
-        <v>1.039130927084559</v>
+        <v>0.9105033763480112</v>
       </c>
       <c r="D102">
-        <v>0.749574517669622</v>
+        <v>0.5657275557594972</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L75</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C103">
-        <v>0.6333670840922766</v>
+        <v>0.545448790840617</v>
       </c>
       <c r="D103">
-        <v>0.4568777756411153</v>
+        <v>0.3389063887625742</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L76</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104">
-        <v>0.6693692425153493</v>
+        <v>1.312868226895126</v>
       </c>
       <c r="D104">
-        <v>0.6092861416349635</v>
+        <v>0.6746808055513193</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L77</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>0.6693692425153493</v>
+        <v>1.063694742547499</v>
       </c>
       <c r="D105">
-        <v>0.6092861416349635</v>
+        <v>0.6609107032521536</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>L78</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>0.19451688279324</v>
+        <v>0.2556852383912203</v>
       </c>
       <c r="D106">
-        <v>0.2806285421749871</v>
+        <v>0.2327347336531229</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>L79</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107">
-        <v>0.7175942382675135</v>
+        <v>0.01764412111384134</v>
       </c>
       <c r="D107">
-        <v>0.5176348244595175</v>
+        <v>0.0160603711571732</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C108">
-        <v>1.14755889450532</v>
+        <v>0.646639833319831</v>
       </c>
       <c r="D108">
-        <v>0.5222765603216356</v>
+        <v>0.360896562527125</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>L80</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C109">
-        <v>0.7022678492315573</v>
+        <v>1.522696720627591</v>
       </c>
       <c r="D109">
-        <v>0.6392317439694251</v>
+        <v>0.7322623358757713</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>L81</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C110">
-        <v>1.038856574934295</v>
+        <v>1.042354091940046</v>
       </c>
       <c r="D110">
-        <v>0.6454778820036224</v>
+        <v>0.5012663597640742</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>L82</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C111">
-        <v>0.6333670840922766</v>
+        <v>0.9213705758897822</v>
       </c>
       <c r="D111">
-        <v>0.4568777756411153</v>
+        <v>0.5142267093957299</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>L83</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C112">
-        <v>0.4555869118836413</v>
+        <v>0.8632649353185766</v>
       </c>
       <c r="D112">
-        <v>0.6572729784684465</v>
+        <v>0.6227140205787212</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>L84</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C113">
-        <v>0.6122032264460429</v>
+        <v>1.569500413738499</v>
       </c>
       <c r="D113">
-        <v>0.8832225588099292</v>
+        <v>0.8759548592840355</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>L85</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6931471805599453</v>
+        <v>1.090392673815928</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0.6085597383702974</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>L86</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0.662192181868297</v>
+        <v>0.887956777501162</v>
       </c>
       <c r="D115">
-        <v>0.9553413768968346</v>
+        <v>0.4955781134416</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>L87</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>0.3732435945336031</v>
+        <v>0.3378188440457618</v>
       </c>
       <c r="D116">
-        <v>0.3397409608316878</v>
+        <v>0.4873695710236627</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>L88</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C117">
-        <v>0.6931471805599453</v>
+        <v>0.490326483433116</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0.3536957930327405</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>L89</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C118">
-        <v>0.662192181868297</v>
+        <v>0.4767868677720328</v>
       </c>
       <c r="D118">
-        <v>0.9553413768968346</v>
+        <v>0.2962443372860183</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B119">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>1.531798519549437</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D119">
-        <v>0.7366393759316762</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>L90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C120">
-        <v>0.662192181868297</v>
+        <v>0.7396268997417544</v>
       </c>
       <c r="D120">
-        <v>0.9553413768968346</v>
+        <v>0.5335280301827539</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>L91</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C121">
-        <v>0.6900175350139677</v>
+        <v>1.176505601032414</v>
       </c>
       <c r="D121">
-        <v>0.6280810274300705</v>
+        <v>0.731004030626492</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>L92</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C122">
-        <v>0.20276290568803</v>
+        <v>1.099677927506998</v>
       </c>
       <c r="D122">
-        <v>0.1845627504620828</v>
+        <v>0.613741937125508</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>L93</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C123">
-        <v>0.5107803845959885</v>
+        <v>1.178466636502206</v>
       </c>
       <c r="D123">
-        <v>0.3684501639199951</v>
+        <v>0.7322224904717841</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>L94</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C124">
-        <v>0.4555869118836413</v>
+        <v>1.197237501557932</v>
       </c>
       <c r="D124">
-        <v>0.6572729784684465</v>
+        <v>0.8636243031319604</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>L95</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C125">
-        <v>0.4555869118836413</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D125">
-        <v>0.6572729784684465</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>L96</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C126">
-        <v>0.662192181868297</v>
+        <v>1.072346228543856</v>
       </c>
       <c r="D126">
-        <v>0.9553413768968346</v>
+        <v>0.6662861737375433</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>L97</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C127">
-        <v>0.6931471805599453</v>
+        <v>1.212240916028029</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0.7532076302307593</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>L98</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>0.662192181868297</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D128">
-        <v>0.9553413768968346</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>L99</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C129">
-        <v>0.662192181868297</v>
+        <v>0.7396268997417544</v>
       </c>
       <c r="D129">
-        <v>0.9553413768968346</v>
+        <v>0.5335280301827539</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130">
-        <v>1.569500413738499</v>
+        <v>1.060836011967138</v>
       </c>
       <c r="D130">
-        <v>0.8759548592840355</v>
+        <v>0.6591344740740812</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MN10</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>1.099677927506998</v>
+        <v>0.7410876939721115</v>
       </c>
       <c r="D131">
-        <v>0.613741937125508</v>
+        <v>0.674567089423841</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MN11</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>1.178466636502206</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D132">
-        <v>0.7322224904717841</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MN110</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133">
-        <v>0.7389811416400135</v>
+        <v>0.4034855815444305</v>
       </c>
       <c r="D133">
-        <v>0.459154799281685</v>
+        <v>0.2910533237821747</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MN111</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B134">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C134">
-        <v>1.113072547203418</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D134">
-        <v>0.6212176167166921</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MN112</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135">
-        <v>1.059361955089344</v>
+        <v>0.7633218389347538</v>
       </c>
       <c r="D135">
-        <v>0.6582185910403799</v>
+        <v>0.5506203158167067</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MN113</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B136">
         <v>4</v>
       </c>
       <c r="C136">
-        <v>0.6729739836656659</v>
+        <v>0.6588267198198127</v>
       </c>
       <c r="D136">
-        <v>0.4854481144408732</v>
+        <v>0.4752430207445932</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MN114</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C137">
-        <v>0.3732435945336031</v>
+        <v>1.246264538116219</v>
       </c>
       <c r="D137">
-        <v>0.3397409608316878</v>
+        <v>0.8989898343880217</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MN115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>0.3732435945336031</v>
+        <v>0.8625295168482716</v>
       </c>
       <c r="D138">
-        <v>0.3397409608316878</v>
+        <v>0.6221835282886775</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MN116</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C139">
-        <v>0.19451688279324</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="D139">
-        <v>0.2806285421749871</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MN117</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>1.04672998205601</v>
+        <v>0.5975603177003802</v>
       </c>
       <c r="D140">
-        <v>0.5841911261152554</v>
+        <v>0.431048653489186</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MN118</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B141">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>0.9081755830687502</v>
+        <v>0.9273112292859568</v>
       </c>
       <c r="D141">
-        <v>0.5068624436850445</v>
+        <v>0.6689136559257491</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MN119</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B142">
         <v>5</v>
       </c>
       <c r="C142">
-        <v>0.862314347241475</v>
+        <v>0.9725640746865342</v>
       </c>
       <c r="D142">
-        <v>0.5357860285130963</v>
+        <v>0.6042880357003871</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MN12</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B143">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C143">
-        <v>1.197237501557932</v>
+        <v>1.076375637939719</v>
       </c>
       <c r="D143">
-        <v>0.8636243031319604</v>
+        <v>0.6687897865608355</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MN120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B144">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C144">
-        <v>1.048179980606054</v>
+        <v>1.322784783614306</v>
       </c>
       <c r="D144">
-        <v>0.5850003857145191</v>
+        <v>0.95418752374187</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MN121</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B145">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C145">
-        <v>1.068652425547084</v>
+        <v>0.8966749151854819</v>
       </c>
       <c r="D145">
-        <v>0.5964262747875932</v>
+        <v>0.6468142267138134</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MN122</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B146">
         <v>5</v>
       </c>
       <c r="C146">
-        <v>1.076018254207006</v>
+        <v>1.220708779190034</v>
       </c>
       <c r="D146">
-        <v>0.6685677315626579</v>
+        <v>0.7584690094343834</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MN123</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C147">
-        <v>0.8866650050430345</v>
+        <v>0.9725640746865342</v>
       </c>
       <c r="D147">
-        <v>0.6395936028526868</v>
+        <v>0.6042880357003871</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MN124</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B148">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C148">
-        <v>1.287673134890783</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D148">
-        <v>0.619239881997626</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MN125</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="C149">
-        <v>1.019056018424425</v>
+        <v>1.039130927084559</v>
       </c>
       <c r="D149">
-        <v>0.7350935320844851</v>
+        <v>0.749574517669622</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MN126</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B150">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C150">
-        <v>1.048792231404724</v>
+        <v>1.021094815861843</v>
       </c>
       <c r="D150">
-        <v>0.9546518296060714</v>
+        <v>0.634441880592677</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MN127</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B151">
         <v>3</v>
       </c>
       <c r="C151">
-        <v>0.8102359754965719</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D151">
-        <v>0.7375085677212407</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MN128</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C152">
-        <v>0.8036765417474231</v>
+        <v>1.095531624518855</v>
       </c>
       <c r="D152">
-        <v>0.7315379138183056</v>
+        <v>0.5629918858538799</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MN129</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C153">
-        <v>0.9869180017300152</v>
+        <v>0.9946503393488847</v>
       </c>
       <c r="D153">
-        <v>0.8983314786388328</v>
+        <v>0.618011003509035</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MN13</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B154">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C154">
-        <v>1.107408753153915</v>
+        <v>1.237596058536554</v>
       </c>
       <c r="D154">
-        <v>0.7988265582060918</v>
+        <v>0.635998563005272</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MN130</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B155">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C155">
-        <v>0.7410876939721115</v>
+        <v>1.237761253347768</v>
       </c>
       <c r="D155">
-        <v>0.674567089423841</v>
+        <v>0.6908077086267796</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MN131</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C156">
-        <v>0.6355993030023191</v>
+        <v>1.121900162570469</v>
       </c>
       <c r="D156">
-        <v>0.5785474180093878</v>
+        <v>0.8092799004564688</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MN132</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B157">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>0.4833021896008116</v>
+        <v>1.336219939197759</v>
       </c>
       <c r="D157">
-        <v>0.4399206112892998</v>
+        <v>0.7457585474759308</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MN133</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C158">
-        <v>0.4555869118836413</v>
+        <v>1.314147081896405</v>
       </c>
       <c r="D158">
-        <v>0.6572729784684465</v>
+        <v>0.8165254911318077</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MN134</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>0.9005509293190957</v>
+      </c>
+      <c r="D159">
+        <v>0.559543752736078</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MN135</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>0.8036765417474231</v>
+        <v>1.091259044341258</v>
       </c>
       <c r="D160">
-        <v>0.7315379138183056</v>
+        <v>0.7871770057981808</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MN136</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B161">
         <v>2</v>
       </c>
       <c r="C161">
-        <v>0.19451688279324</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D161">
-        <v>0.2806285421749871</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MN137</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C162">
-        <v>0.19451688279324</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D162">
-        <v>0.2806285421749871</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MN138</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>0.4555869118836413</v>
+        <v>1.21834612096083</v>
       </c>
       <c r="D163">
-        <v>0.6572729784684465</v>
+        <v>0.8788509533982471</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MN139</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B164">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C164">
-        <v>0.19451688279324</v>
+        <v>1.173705180235459</v>
       </c>
       <c r="D164">
-        <v>0.2806285421749871</v>
+        <v>0.8466493214956918</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MN14</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165">
-        <v>1.072346228543856</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D165">
-        <v>0.6662861737375433</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MN140</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B166">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C166">
-        <v>0.2449300267946353</v>
+        <v>1.321088769299851</v>
       </c>
       <c r="D166">
-        <v>0.3533593350214213</v>
+        <v>0.9529641080214998</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MN141</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C167">
-        <v>0.607271814155035</v>
+        <v>1.301464101246379</v>
       </c>
       <c r="D167">
-        <v>0.5527626264687555</v>
+        <v>0.9388079023815816</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MN15</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B168">
         <v>5</v>
       </c>
       <c r="C168">
-        <v>1.212240916028029</v>
+        <v>0.5116118989174834</v>
       </c>
       <c r="D168">
-        <v>0.7532076302307593</v>
+        <v>0.3178823457338133</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MN16</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B169">
         <v>3</v>
       </c>
       <c r="C169">
-        <v>0.2269283709027674</v>
+        <v>0.673030158126667</v>
       </c>
       <c r="D169">
-        <v>0.2065591048302231</v>
+        <v>0.6126184506297554</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MN17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B170">
         <v>4</v>
       </c>
       <c r="C170">
-        <v>0.7396268997417544</v>
+        <v>1.020592004227205</v>
       </c>
       <c r="D170">
-        <v>0.5335280301827539</v>
+        <v>0.7362015116347587</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MN18</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171">
-        <v>1.060836011967138</v>
+        <v>1.130808521297513</v>
       </c>
       <c r="D171">
-        <v>0.6591344740740812</v>
+        <v>0.8157059229354519</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MN19</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C172">
-        <v>0.7410876939721115</v>
+        <v>1.123266013178042</v>
       </c>
       <c r="D172">
-        <v>0.674567089423841</v>
+        <v>0.6979244147910146</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MN2</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B173">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C173">
-        <v>1.090392673815928</v>
+        <v>0.8632649353185766</v>
       </c>
       <c r="D173">
-        <v>0.6085597383702974</v>
+        <v>0.6227140205787212</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MN20</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C174">
-        <v>0.6931471805599453</v>
+        <v>0.1895074258256648</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>0.1367007117251599</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MN21</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C175">
-        <v>0.4034855815444305</v>
+        <v>0.846059662603294</v>
       </c>
       <c r="D175">
-        <v>0.2910533237821747</v>
+        <v>0.7701166929681853</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MN22</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B176">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C176">
-        <v>0.6333670840922766</v>
+        <v>0.997013883990751</v>
       </c>
       <c r="D176">
-        <v>0.4568777756411153</v>
+        <v>0.5564440434743706</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MN23</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B177">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C177">
-        <v>0.7633218389347538</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D177">
-        <v>0.5506203158167067</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MN24</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C178">
-        <v>0.6588267198198127</v>
+        <v>1.157836493449356</v>
       </c>
       <c r="D178">
-        <v>0.4752430207445932</v>
+        <v>0.4659476819976865</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MN25</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B179">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C179">
-        <v>1.246264538116219</v>
+        <v>1.218987605137656</v>
       </c>
       <c r="D179">
-        <v>0.8989898343880217</v>
+        <v>0.6803299360615819</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MN26</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C180">
-        <v>0.8625295168482716</v>
+        <v>1.193289014574816</v>
       </c>
       <c r="D180">
-        <v>0.6221835282886775</v>
+        <v>0.7414321517815469</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MN27</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B181">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C181">
-        <v>1.386294361119891</v>
+        <v>0.627941588739906</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>0.9059282160429994</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MN28</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B182">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C182">
-        <v>0.5975603177003802</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D182">
-        <v>0.431048653489186</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MN29</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B183">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C183">
-        <v>0.9273112292859568</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D183">
-        <v>0.6689136559257491</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MN3</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B184">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C184">
-        <v>0.887956777501162</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D184">
-        <v>0.4955781134416</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MN30</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B185">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C185">
-        <v>0.9725640746865342</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D185">
-        <v>0.6042880357003871</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MN31</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B186">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C186">
-        <v>1.076375637939719</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D186">
-        <v>0.6687897865608355</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MN32</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B187">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>1.322784783614306</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D187">
-        <v>0.95418752374187</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MN33</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B188">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C188">
-        <v>0.8966749151854819</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D188">
-        <v>0.6468142267138134</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MN34</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B189">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C189">
-        <v>1.220708779190034</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D189">
-        <v>0.7584690094343834</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MN35</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B190">
         <v>5</v>
       </c>
       <c r="C190">
-        <v>0.9725640746865342</v>
+        <v>0.7389811416400135</v>
       </c>
       <c r="D190">
-        <v>0.6042880357003871</v>
+        <v>0.459154799281685</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MN36</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B191">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C191">
-        <v>0.6333670840922766</v>
+        <v>1.113072547203418</v>
       </c>
       <c r="D191">
-        <v>0.4568777756411153</v>
+        <v>0.6212176167166921</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MN37</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C192">
-        <v>1.039130927084559</v>
+        <v>1.059361955089344</v>
       </c>
       <c r="D192">
-        <v>0.749574517669622</v>
+        <v>0.6582185910403799</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MN38</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193">
-        <v>1.021094815861843</v>
+        <v>0.6729739836656659</v>
       </c>
       <c r="D193">
-        <v>0.634441880592677</v>
+        <v>0.4854481144408732</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MN39</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B194">
         <v>3</v>
       </c>
       <c r="C194">
-        <v>0.2269283709027674</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D194">
-        <v>0.2065591048302231</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MN4</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C195">
-        <v>0.3378188440457618</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D195">
-        <v>0.4873695710236627</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MN40</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B196">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C196">
-        <v>1.095531624518855</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D196">
-        <v>0.5629918858538799</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MN41</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C197">
-        <v>0.9946503393488847</v>
+        <v>1.04672998205601</v>
       </c>
       <c r="D197">
-        <v>0.618011003509035</v>
+        <v>0.5841911261152554</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MN42</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B198">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C198">
-        <v>1.237596058536554</v>
+        <v>0.9081755830687502</v>
       </c>
       <c r="D198">
-        <v>0.635998563005272</v>
+        <v>0.5068624436850445</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MN43</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C199">
-        <v>1.237761253347768</v>
+        <v>0.862314347241475</v>
       </c>
       <c r="D199">
-        <v>0.6908077086267796</v>
+        <v>0.5357860285130963</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MN44</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B200">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C200">
-        <v>1.121900162570469</v>
+        <v>1.048179980606054</v>
       </c>
       <c r="D200">
-        <v>0.8092799004564688</v>
+        <v>0.5850003857145191</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MN45</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B201">
         <v>6</v>
       </c>
       <c r="C201">
-        <v>1.336219939197759</v>
+        <v>1.068652425547084</v>
       </c>
       <c r="D201">
-        <v>0.7457585474759308</v>
+        <v>0.5964262747875932</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MN46</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B202">
         <v>5</v>
       </c>
       <c r="C202">
-        <v>1.314147081896405</v>
+        <v>1.076018254207006</v>
       </c>
       <c r="D202">
-        <v>0.8165254911318077</v>
+        <v>0.6685677315626579</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MN47</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B203">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>0.9005509293190957</v>
+        <v>0.8866650050430345</v>
       </c>
       <c r="D203">
-        <v>0.559543752736078</v>
+        <v>0.6395936028526868</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MN48</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B204">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C204">
-        <v>1.091259044341258</v>
+        <v>1.287673134890783</v>
       </c>
       <c r="D204">
-        <v>0.7871770057981808</v>
+        <v>0.619239881997626</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MN49</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B205">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C205">
-        <v>0.6931471805599453</v>
+        <v>1.019056018424425</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0.7350935320844851</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MN5</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C206">
-        <v>0.490326483433116</v>
+        <v>1.048792231404724</v>
       </c>
       <c r="D206">
-        <v>0.3536957930327405</v>
+        <v>0.9546518296060714</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MN50</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207">
-        <v>1.107408753153915</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D207">
-        <v>0.7988265582060918</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MN51</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C208">
-        <v>1.21834612096083</v>
+        <v>0.8036765417474231</v>
       </c>
       <c r="D208">
-        <v>0.8788509533982471</v>
+        <v>0.7315379138183056</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MN52</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C209">
-        <v>1.173705180235459</v>
+        <v>0.9869180017300152</v>
       </c>
       <c r="D209">
-        <v>0.8466493214956918</v>
+        <v>0.8983314786388328</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MN53</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C210">
-        <v>1.107408753153915</v>
+        <v>0.7410876939721115</v>
       </c>
       <c r="D210">
-        <v>0.7988265582060918</v>
+        <v>0.674567089423841</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MN54</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>1.321088769299851</v>
+        <v>0.6355993030023191</v>
       </c>
       <c r="D211">
-        <v>0.9529641080214998</v>
+        <v>0.5785474180093878</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MN55</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B212">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212">
-        <v>1.301464101246379</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D212">
-        <v>0.9388079023815816</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MN56</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B213">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>0.5116118989174834</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D213">
-        <v>0.3178823457338133</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MN57</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>0.673030158126667</v>
-      </c>
-      <c r="D214">
-        <v>0.6126184506297554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MN58</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>1.020592004227205</v>
+        <v>0.8036765417474231</v>
       </c>
       <c r="D215">
-        <v>0.7362015116347587</v>
+        <v>0.7315379138183056</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MN59</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B216">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C216">
-        <v>1.130808521297513</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D216">
-        <v>0.8157059229354519</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MN6</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B217">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C217">
-        <v>0.4767868677720328</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D217">
-        <v>0.2962443372860183</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MN60</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B218">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C218">
-        <v>1.123266013178042</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D218">
-        <v>0.6979244147910146</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MN61</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B219">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C219">
-        <v>0.8632649353185766</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D219">
-        <v>0.6227140205787212</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MN62</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B220">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C220">
-        <v>0.1895074258256648</v>
+        <v>0.2449300267946353</v>
       </c>
       <c r="D220">
-        <v>0.1367007117251599</v>
+        <v>0.3533593350214213</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MN63</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B221">
         <v>3</v>
       </c>
       <c r="C221">
-        <v>0.846059662603294</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D221">
-        <v>0.7701166929681853</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MN64</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B222">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C222">
-        <v>0.997013883990751</v>
+        <v>1.156027655202271</v>
       </c>
       <c r="D222">
-        <v>0.5564440434743706</v>
+        <v>0.4652197519375215</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MN65</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C223">
-        <v>0.3732435945336031</v>
+        <v>0.9683146857576469</v>
       </c>
       <c r="D223">
-        <v>0.3397409608316878</v>
+        <v>0.3775180523314358</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MN66</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B224">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C224">
-        <v>1.157836493449356</v>
+        <v>0.5216705256352127</v>
       </c>
       <c r="D224">
-        <v>0.4659476819976865</v>
+        <v>0.2508704934372867</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MN67</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B225">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C225">
-        <v>1.218987605137656</v>
+        <v>0.4034855815444305</v>
       </c>
       <c r="D225">
-        <v>0.6803299360615819</v>
+        <v>0.2910533237821747</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MN68</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B226">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C226">
-        <v>1.193289014574816</v>
+        <v>1.213630920484374</v>
       </c>
       <c r="D226">
-        <v>0.7414321517815469</v>
+        <v>0.6236829182855944</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MN69</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C227">
-        <v>0.627941588739906</v>
+        <v>0.5081267731378364</v>
       </c>
       <c r="D227">
-        <v>0.9059282160429994</v>
+        <v>0.2044852562896828</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MN7</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C228">
-        <v>0.4555869118836413</v>
+        <v>1.184605387662923</v>
       </c>
       <c r="D228">
-        <v>0.6572729784684465</v>
+        <v>0.5391371459621421</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MN70</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C229">
-        <v>0.4555869118836413</v>
+        <v>1.14755889450532</v>
       </c>
       <c r="D229">
-        <v>0.6572729784684465</v>
+        <v>0.5222765603216356</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MN71</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C230">
-        <v>0.662192181868297</v>
+        <v>1.531798519549437</v>
       </c>
       <c r="D230">
-        <v>0.9553413768968346</v>
+        <v>0.7366393759316762</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MN72</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C231">
-        <v>0.6931471805599453</v>
+        <v>0.836386862720723</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0.6033255895559327</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MN73</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B232">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C232">
-        <v>0.662192181868297</v>
+        <v>1.068652425547084</v>
       </c>
       <c r="D232">
-        <v>0.9553413768968346</v>
+        <v>0.5964262747875932</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MN74</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C233">
-        <v>0.662192181868297</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D233">
-        <v>0.9553413768968346</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MN75</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>0.662192181868297</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D234">
-        <v>0.9553413768968346</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>MN76</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C235">
-        <v>0.662192181868297</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D235">
-        <v>0.9553413768968346</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MN77</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B236">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C236">
-        <v>0.607271814155035</v>
+        <v>0.8170082613435337</v>
       </c>
       <c r="D236">
-        <v>0.5527626264687555</v>
+        <v>0.5893468835028152</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MN8</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C237">
-        <v>0.7396268997417544</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D237">
-        <v>0.5335280301827539</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MN9</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B238">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C238">
-        <v>1.176505601032414</v>
+        <v>1.430458048303307</v>
       </c>
       <c r="D238">
-        <v>0.731004030626492</v>
+        <v>0.6510295138048688</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MT1</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B239">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C239">
-        <v>1.020592004227205</v>
+        <v>1.02998864247627</v>
       </c>
       <c r="D239">
-        <v>0.7362015116347587</v>
+        <v>0.9375360653620259</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MT10</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C240">
-        <v>0.640185309289103</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D240">
-        <v>0.4617960854806781</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MT100</t>
+          <t>241</t>
         </is>
       </c>
       <c r="B241">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C241">
-        <v>1.106494586142389</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D241">
-        <v>0.6175463867474918</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MT101</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B242">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C242">
-        <v>0.9105033763480112</v>
+        <v>0.6900175350139677</v>
       </c>
       <c r="D242">
-        <v>0.5657275557594972</v>
+        <v>0.6280810274300705</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MT102</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B243">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C243">
-        <v>0.545448790840617</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D243">
-        <v>0.3389063887625742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MT103</t>
+          <t>244</t>
         </is>
       </c>
       <c r="B244">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C244">
-        <v>1.312868226895126</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D244">
-        <v>0.6746808055513193</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MT104</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B245">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C245">
-        <v>1.063694742547499</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D245">
-        <v>0.6609107032521536</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MT105</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B246">
         <v>3</v>
       </c>
       <c r="C246">
-        <v>0.2556852383912203</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D246">
-        <v>0.2327347336531229</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MT106</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C247">
-        <v>0.01764412111384134</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D247">
-        <v>0.0160603711571732</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MT107</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B248">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C248">
-        <v>0.646639833319831</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D248">
-        <v>0.360896562527125</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MT108</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B249">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C249">
-        <v>1.522696720627591</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D249">
-        <v>0.7322623358757713</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MT109</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B250">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C250">
-        <v>1.042354091940046</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D250">
-        <v>0.5012663597640742</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MT11</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B251">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C251">
-        <v>0.4281198529765204</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D251">
-        <v>0.266005820832837</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MT110</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B252">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C252">
-        <v>0.9213705758897822</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D252">
-        <v>0.5142267093957299</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MT111</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B253">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C253">
-        <v>0.8632649353185766</v>
+        <v>0.5380247029595945</v>
       </c>
       <c r="D253">
-        <v>0.6227140205787212</v>
+        <v>0.3342935436048542</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MT12</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B254">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C254">
-        <v>0.9023690239276578</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D254">
-        <v>0.5036217413247025</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MT13</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B255">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C255">
-        <v>0.4767868677720328</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D255">
-        <v>0.2962443372860183</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MT14</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B256">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C256">
-        <v>0.03423054971755033</v>
+        <v>0.2351010815977794</v>
       </c>
       <c r="D256">
-        <v>0.04938424432441297</v>
+        <v>0.169589582264374</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MT15</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B257">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C257">
-        <v>0.06811529608647736</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D257">
-        <v>0.06200121443121319</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MT16</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B258">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C258">
-        <v>0.8676768615147434</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D258">
-        <v>0.5391179459681525</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MT17</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B259">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C259">
-        <v>1.030966024605707</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D259">
-        <v>0.7436847855118315</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MT18</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B260">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C260">
-        <v>0.9021241814080119</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D260">
-        <v>0.6507450413916772</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MT19</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B261">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C261">
-        <v>0.708018976056273</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D261">
-        <v>0.6444666452025871</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MT2</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B262">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C262">
-        <v>1.039635030233855</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D262">
-        <v>0.6459615634762322</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MT20</t>
+          <t>264</t>
         </is>
       </c>
       <c r="B263">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C263">
-        <v>0.08671091094332455</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D263">
-        <v>0.05387651817657488</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MT21</t>
+          <t>265</t>
         </is>
       </c>
       <c r="B264">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C264">
-        <v>0.3682207759404497</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D264">
-        <v>0.2287884317224488</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MT22</t>
+          <t>266</t>
         </is>
       </c>
       <c r="B265">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C265">
-        <v>1.364827789086023</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D265">
-        <v>0.6563434276606179</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MT23</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B266">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C266">
-        <v>0.7290149744224851</v>
+        <v>0.4626659965444074</v>
       </c>
       <c r="D266">
-        <v>0.4529624714257719</v>
+        <v>0.4211367388811164</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MT24</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B267">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C267">
-        <v>0.773826687226959</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D267">
-        <v>0.4318808972503141</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MT25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B268">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C268">
-        <v>1.359443731813305</v>
+        <v>0.2590219627222835</v>
       </c>
       <c r="D268">
-        <v>0.6537542434182135</v>
+        <v>0.1868448505503822</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MT26</t>
+          <t>270</t>
         </is>
       </c>
       <c r="B269">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C269">
-        <v>1.509153859937444</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D269">
-        <v>0.6868455211651825</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MT27</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B270">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C270">
-        <v>0.9079997485322008</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D270">
-        <v>0.5067643085616815</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MT28</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C271">
-        <v>0.7173630342061832</v>
+        <v>1.048792231404724</v>
       </c>
       <c r="D271">
-        <v>0.5174680459831602</v>
+        <v>0.9546518296060714</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MT29</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B272">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C272">
-        <v>0.9416329786242219</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D272">
-        <v>0.4528297428662228</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MT3</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B273">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C273">
-        <v>1.476352099299954</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D273">
-        <v>0.758694896584348</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MT30</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B274">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C274">
-        <v>0.7347804129124217</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D274">
-        <v>0.3776024362014544</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MT31</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B275">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C275">
-        <v>0.7926128795467399</v>
+        <v>0.5638225808048839</v>
       </c>
       <c r="D275">
-        <v>0.5717493353334014</v>
+        <v>0.513213429906585</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MT32</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B276">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C276">
-        <v>0.9739004879384758</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D276">
-        <v>0.6051183959408269</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MT33</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C277">
-        <v>0.7278048664104161</v>
+        <v>0.5975603177003802</v>
       </c>
       <c r="D277">
-        <v>0.6624765387366658</v>
+        <v>0.431048653489186</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MT34</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B278">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C278">
-        <v>0.1649791295575473</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D278">
-        <v>0.1190072860314256</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MT35</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C279">
-        <v>0.6211056731868858</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D279">
-        <v>0.5653547476151721</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MT36</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C280">
-        <v>0.7728200659624421</v>
+        <v>0.7280100277746424</v>
       </c>
       <c r="D280">
-        <v>0.5574718383317484</v>
+        <v>0.6626632846581728</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MT37</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B281">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C281">
-        <v>1.019056018424425</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D281">
-        <v>0.7350935320844851</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MT38</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B282">
         <v>2</v>
       </c>
       <c r="C282">
-        <v>0.5004024235381879</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D282">
-        <v>0.7219280948873623</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MT39</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B283">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C283">
-        <v>0.9887339357979354</v>
+        <v>1.365304352400869</v>
       </c>
       <c r="D283">
-        <v>0.4754805153114361</v>
+        <v>0.7619908675515937</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MT4</t>
+          <t>285</t>
         </is>
       </c>
       <c r="B284">
         <v>6</v>
       </c>
       <c r="C284">
-        <v>1.206337125031212</v>
+        <v>1.218987605137656</v>
       </c>
       <c r="D284">
-        <v>0.6732695686832003</v>
+        <v>0.6803299360615819</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MT40</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B285">
         <v>6</v>
       </c>
       <c r="C285">
-        <v>0.8674284029982893</v>
+        <v>1.245446142364597</v>
       </c>
       <c r="D285">
-        <v>0.4841210094857231</v>
+        <v>0.695096726850939</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MT41</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B286">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C286">
-        <v>0.9477353118178559</v>
+        <v>1.213579666667576</v>
       </c>
       <c r="D286">
-        <v>0.4870396057484749</v>
+        <v>0.7540394427717741</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MT42</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B287">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C287">
-        <v>0.8568847365088091</v>
+        <v>1.228890586157654</v>
       </c>
       <c r="D287">
-        <v>0.6181116799873525</v>
+        <v>0.763552651931189</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MT43</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B288">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C288">
-        <v>0.3972454932559829</v>
+        <v>1.715612302311079</v>
       </c>
       <c r="D288">
-        <v>0.3615884305623224</v>
+        <v>0.6688679046704358</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MT44</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B289">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C289">
-        <v>0.502262918546141</v>
+        <v>1.096342189139819</v>
       </c>
       <c r="D289">
-        <v>0.3623061109044675</v>
+        <v>0.4761353630211544</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MT45</t>
+          <t>291</t>
         </is>
       </c>
       <c r="B290">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C290">
-        <v>0.0118011300326326</v>
+        <v>1.515376040227951</v>
       </c>
       <c r="D290">
-        <v>0.01702543177496486</v>
+        <v>0.6581194522793991</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MT46</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B291">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C291">
-        <v>0.0576346077189195</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D291">
-        <v>0.05246128075701044</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MT47</t>
+          <t>293</t>
         </is>
       </c>
       <c r="B292">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C292">
-        <v>0.2664108619040347</v>
+        <v>1.25279924147191</v>
       </c>
       <c r="D292">
-        <v>0.1921748146539526</v>
+        <v>0.7784079347162806</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MT48</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B293">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C293">
-        <v>0.4706255754642422</v>
+        <v>0.2351010815977794</v>
       </c>
       <c r="D293">
-        <v>0.2924161111331546</v>
+        <v>0.169589582264374</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MT49</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B294">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C294">
-        <v>0.08082938714559725</v>
+        <v>1.039130927084559</v>
       </c>
       <c r="D294">
-        <v>0.05022212197260319</v>
+        <v>0.749574517669622</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B295">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C295">
-        <v>1.219152983197208</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D295">
-        <v>0.5862886543145326</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MT50</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B296">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C296">
-        <v>0.5485892608214828</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D296">
-        <v>0.3061734960763634</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MT51</t>
+          <t>298</t>
         </is>
       </c>
       <c r="B297">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C297">
-        <v>0.3682207759404497</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D297">
-        <v>0.2287884317224488</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MT52</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B298">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C298">
-        <v>0.4857472289679715</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D298">
-        <v>0.2711006903048467</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MT53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B299">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C299">
-        <v>0.4281198529765204</v>
+        <v>0.7175942382675135</v>
       </c>
       <c r="D299">
-        <v>0.266005820832837</v>
+        <v>0.5176348244595175</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MT54</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B300">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C300">
-        <v>1.285293024120099</v>
+        <v>0.7022678492315573</v>
       </c>
       <c r="D300">
-        <v>0.9271429359936232</v>
+        <v>0.6392317439694251</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MT55</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B301">
         <v>5</v>
       </c>
       <c r="C301">
-        <v>0.862314347241475</v>
+        <v>1.038856574934295</v>
       </c>
       <c r="D301">
-        <v>0.5357860285130963</v>
+        <v>0.6454778820036224</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MT56</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C302">
-        <v>0.511172191333868</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D302">
-        <v>0.3176091400511223</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MT57</t>
+          <t>304</t>
         </is>
       </c>
       <c r="B303">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C303">
-        <v>0.4434581029780121</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D303">
-        <v>0.2474986797022859</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MT58</t>
+          <t>305</t>
         </is>
       </c>
       <c r="B304">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C304">
-        <v>0.4410441397088374</v>
+        <v>0.6122032264460429</v>
       </c>
       <c r="D304">
-        <v>0.2461514211496551</v>
+        <v>0.8832225588099292</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MT59</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B305">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C305">
-        <v>1.039130927084559</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D305">
-        <v>0.749574517669622</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MT6</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B306">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C306">
-        <v>1.240240595784448</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D306">
-        <v>0.7706048094199043</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MT60</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B307">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C307">
-        <v>0.7406479077512897</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D307">
-        <v>0.4133634678489427</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MT61</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B308">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C308">
-        <v>0.2752067937223205</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D308">
-        <v>0.1535958360755242</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MT62</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B309">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C309">
-        <v>0.6349755035427602</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D309">
-        <v>0.4580380050235563</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MT63</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B310">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C310">
-        <v>0.4396636161300515</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D310">
-        <v>0.2259424035295239</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MT64</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B311">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C311">
-        <v>0.3534440494092194</v>
+        <v>0.6900175350139677</v>
       </c>
       <c r="D311">
-        <v>0.1816343111118501</v>
+        <v>0.6280810274300705</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MT65</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B312">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C312">
-        <v>0.8788267410129095</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D312">
-        <v>0.546045755616493</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MT66</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B313">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C313">
-        <v>1.173252423569263</v>
+        <v>0.5107803845959885</v>
       </c>
       <c r="D313">
-        <v>0.564215151064778</v>
+        <v>0.3684501639199951</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>MT67</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B314">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C314">
-        <v>1.49181149092682</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D314">
-        <v>0.7666394523154394</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MT68</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B315">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C315">
-        <v>1.704568598372718</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D315">
-        <v>0.7402847362988317</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MT69</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B316">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C316">
-        <v>0.8369882167858358</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D316">
-        <v>0.603759374819711</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>MT7</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B317">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C317">
-        <v>1.506428853865558</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D317">
-        <v>0.7244391456412952</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MT70</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B318">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C318">
-        <v>0.2846002445573275</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D318">
-        <v>0.1588384208065282</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MT71</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B319">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C319">
-        <v>0.3972454932559829</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D319">
-        <v>0.3615884305623224</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>MT72</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B320">
         <v>5</v>
       </c>
       <c r="C320">
-        <v>0.6474509497201001</v>
+        <v>0.9266767387691077</v>
       </c>
       <c r="D320">
-        <v>0.4022838934748969</v>
+        <v>0.575776630841018</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>MT73</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B321">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C321">
-        <v>1.167927660369051</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D321">
-        <v>0.6518328382951034</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MT74</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B322">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C322">
-        <v>1.146046065801054</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D322">
-        <v>0.5511316585871623</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>MT75</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B323">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C323">
-        <v>1.456984643522396</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D323">
-        <v>0.7006615066203783</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MT76</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B324">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C324">
-        <v>1.098136135936212</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D324">
-        <v>0.5643303399539427</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MT77</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B325">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C325">
-        <v>1.470647910959634</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D325">
-        <v>0.8207842270219642</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MT78</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B326">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C326">
-        <v>1.048585831905833</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D326">
-        <v>0.5852268956377251</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MT79</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B327">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C327">
-        <v>0.6790268485207671</v>
+        <v>0.755017152900669</v>
       </c>
       <c r="D327">
-        <v>0.489814333495686</v>
+        <v>0.4213830962623312</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MT8</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B328">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C328">
-        <v>0.9734863771041283</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D328">
-        <v>0.6048610944126672</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MT80</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B329">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C329">
-        <v>0.966329936545508</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D329">
-        <v>0.496595352573003</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MT81</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B330">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C330">
-        <v>0.6947669929073684</v>
-      </c>
-      <c r="D330">
-        <v>0.4316830040722781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MT82</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B331">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C331">
-        <v>1.240924692823335</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D331">
-        <v>0.6925732578145454</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>MT83</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B332">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C332">
-        <v>1.312868226895126</v>
+        <v>1.121900162570469</v>
       </c>
       <c r="D332">
-        <v>0.6746808055513193</v>
+        <v>0.8092799004564688</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MT84</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B333">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C333">
-        <v>0.6446717045884102</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D333">
-        <v>0.4005570513828732</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>MT85</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B334">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C334">
-        <v>0.615988059031729</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D334">
-        <v>0.2803482472322038</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MT86</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B335">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C335">
-        <v>1.240931968485071</v>
-      </c>
-      <c r="D335">
-        <v>0.771034383431602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MT87</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B336">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C336">
-        <v>1.646112134736446</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D336">
-        <v>0.7491779182317774</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MT88</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B337">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C337">
-        <v>1.08431193273859</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D337">
-        <v>0.5572261048461018</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MT89</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B338">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C338">
-        <v>1.723836118994475</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D338">
-        <v>0.9620912564436768</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MT9</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B339">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C339">
-        <v>0.7934541620946818</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D339">
-        <v>0.4930007898811508</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MT90</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B340">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C340">
-        <v>1.229398558534492</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D340">
-        <v>0.5126990208791605</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MT91</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B341">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C341">
-        <v>0.4127157986058386</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D341">
-        <v>0.2977115179725858</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MT92</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B342">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C342">
-        <v>0.103483417174611</v>
+        <v>0.9485670767867524</v>
       </c>
       <c r="D342">
-        <v>0.0746475063860275</v>
+        <v>0.5294053655513394</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MT93</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B343">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C343">
-        <v>1.231325910644499</v>
+        <v>0.4127157986058386</v>
       </c>
       <c r="D343">
-        <v>0.7650658041118541</v>
+        <v>0.2977115179725858</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>MT94</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B344">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C344">
-        <v>0.7870187704033657</v>
+        <v>0.00883143005016138</v>
       </c>
       <c r="D344">
-        <v>0.404447641524169</v>
+        <v>0.01274106033732559</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>MT95</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B345">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C345">
-        <v>1.402665586529982</v>
+        <v>1.247010772072043</v>
       </c>
       <c r="D345">
-        <v>0.7208275198168519</v>
+        <v>0.7748113564605138</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>MT96</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B346">
         <v>5</v>
       </c>
       <c r="C346">
-        <v>1.096307977892248</v>
+        <v>0.2771070250309874</v>
       </c>
       <c r="D346">
-        <v>0.6811744457008606</v>
+        <v>0.1721762752636373</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MT97</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B347">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C347">
-        <v>0.9654366173391478</v>
+        <v>0.6446717045884102</v>
       </c>
       <c r="D347">
-        <v>0.5388204353986685</v>
+        <v>0.4005570513828732</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>MT98</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B348">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C348">
-        <v>1.549290658738799</v>
+        <v>1.39837008467158</v>
       </c>
       <c r="D348">
-        <v>0.7450513167526869</v>
+        <v>0.7186200685321729</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>MT99</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B349">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C349">
-        <v>1.63956968219039</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D349">
-        <v>0.7462003197588951</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
   </sheetData>

--- a/Vegetation/Ergebnisse_species_richness.xlsx
+++ b/Vegetation/Ergebnisse_species_richness.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2155,1175 +2155,1175 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113">
         <v>6</v>
       </c>
       <c r="C113">
-        <v>1.569500413738499</v>
+        <v>1.126666445063096</v>
       </c>
       <c r="D113">
-        <v>0.8759548592840355</v>
+        <v>0.6288045155684309</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>1.090392673815928</v>
+        <v>1.569500413738499</v>
       </c>
       <c r="D114">
-        <v>0.6085597383702974</v>
+        <v>0.8759548592840355</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.887956777501162</v>
+        <v>1.090392673815928</v>
       </c>
       <c r="D115">
-        <v>0.4955781134416</v>
+        <v>0.6085597383702974</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C116">
-        <v>0.3378188440457618</v>
+        <v>0.887956777501162</v>
       </c>
       <c r="D116">
-        <v>0.4873695710236627</v>
+        <v>0.4955781134416</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>0.490326483433116</v>
+        <v>0.3378188440457618</v>
       </c>
       <c r="D117">
-        <v>0.3536957930327405</v>
+        <v>0.4873695710236627</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
-        <v>0.4767868677720328</v>
+        <v>0.490326483433116</v>
       </c>
       <c r="D118">
-        <v>0.2962443372860183</v>
+        <v>0.3536957930327405</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C119">
-        <v>0.4555869118836413</v>
+        <v>0.4767868677720328</v>
       </c>
       <c r="D119">
-        <v>0.6572729784684465</v>
+        <v>0.2962443372860183</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>0.7396268997417544</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D120">
-        <v>0.5335280301827539</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121">
-        <v>1.176505601032414</v>
+        <v>0.7396268997417544</v>
       </c>
       <c r="D121">
-        <v>0.731004030626492</v>
+        <v>0.5335280301827539</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122">
-        <v>1.099677927506998</v>
+        <v>1.176505601032414</v>
       </c>
       <c r="D122">
-        <v>0.613741937125508</v>
+        <v>0.731004030626492</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C123">
-        <v>1.178466636502206</v>
+        <v>1.099677927506998</v>
       </c>
       <c r="D123">
-        <v>0.7322224904717841</v>
+        <v>0.613741937125508</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C124">
-        <v>1.197237501557932</v>
+        <v>1.178466636502206</v>
       </c>
       <c r="D124">
-        <v>0.8636243031319604</v>
+        <v>0.7322224904717841</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125">
-        <v>1.107408753153915</v>
+        <v>1.197237501557932</v>
       </c>
       <c r="D125">
-        <v>0.7988265582060918</v>
+        <v>0.8636243031319604</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126">
-        <v>1.072346228543856</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D126">
-        <v>0.6662861737375433</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127">
         <v>5</v>
       </c>
       <c r="C127">
-        <v>1.212240916028029</v>
+        <v>1.072346228543856</v>
       </c>
       <c r="D127">
-        <v>0.7532076302307593</v>
+        <v>0.6662861737375433</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C128">
-        <v>0.2269283709027674</v>
+        <v>1.212240916028029</v>
       </c>
       <c r="D128">
-        <v>0.2065591048302231</v>
+        <v>0.7532076302307593</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>0.7396268997417544</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D129">
-        <v>0.5335280301827539</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
-        <v>1.060836011967138</v>
+        <v>0.7396268997417544</v>
       </c>
       <c r="D130">
-        <v>0.6591344740740812</v>
+        <v>0.5335280301827539</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C131">
-        <v>0.7410876939721115</v>
+        <v>1.060836011967138</v>
       </c>
       <c r="D131">
-        <v>0.674567089423841</v>
+        <v>0.6591344740740812</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>0.6931471805599453</v>
+        <v>0.7410876939721115</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>0.674567089423841</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>0.4034855815444305</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D133">
-        <v>0.2910533237821747</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134">
         <v>4</v>
       </c>
       <c r="C134">
-        <v>0.6333670840922766</v>
+        <v>0.4034855815444305</v>
       </c>
       <c r="D134">
-        <v>0.4568777756411153</v>
+        <v>0.2910533237821747</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135">
         <v>4</v>
       </c>
       <c r="C135">
-        <v>0.7633218389347538</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D135">
-        <v>0.5506203158167067</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136">
         <v>4</v>
       </c>
       <c r="C136">
-        <v>0.6588267198198127</v>
+        <v>0.7633218389347538</v>
       </c>
       <c r="D136">
-        <v>0.4752430207445932</v>
+        <v>0.5506203158167067</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
       <c r="C137">
-        <v>1.246264538116219</v>
+        <v>0.6588267198198127</v>
       </c>
       <c r="D137">
-        <v>0.8989898343880217</v>
+        <v>0.4752430207445932</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138">
         <v>4</v>
       </c>
       <c r="C138">
-        <v>0.8625295168482716</v>
+        <v>1.246264538116219</v>
       </c>
       <c r="D138">
-        <v>0.6221835282886775</v>
+        <v>0.8989898343880217</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139">
         <v>4</v>
       </c>
       <c r="C139">
-        <v>1.386294361119891</v>
+        <v>0.8625295168482716</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>0.6221835282886775</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140">
         <v>4</v>
       </c>
       <c r="C140">
-        <v>0.5975603177003802</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="D140">
-        <v>0.431048653489186</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141">
         <v>4</v>
       </c>
       <c r="C141">
-        <v>0.9273112292859568</v>
+        <v>0.5975603177003802</v>
       </c>
       <c r="D141">
-        <v>0.6689136559257491</v>
+        <v>0.431048653489186</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
-        <v>0.9725640746865342</v>
+        <v>0.9273112292859568</v>
       </c>
       <c r="D142">
-        <v>0.6042880357003871</v>
+        <v>0.6689136559257491</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143">
         <v>5</v>
       </c>
       <c r="C143">
-        <v>1.076375637939719</v>
+        <v>0.9725640746865342</v>
       </c>
       <c r="D143">
-        <v>0.6687897865608355</v>
+        <v>0.6042880357003871</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144">
-        <v>1.322784783614306</v>
+        <v>1.076375637939719</v>
       </c>
       <c r="D144">
-        <v>0.95418752374187</v>
+        <v>0.6687897865608355</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145">
-        <v>0.8966749151854819</v>
+        <v>1.322784783614306</v>
       </c>
       <c r="D145">
-        <v>0.6468142267138134</v>
+        <v>0.95418752374187</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146">
-        <v>1.220708779190034</v>
+        <v>0.8966749151854819</v>
       </c>
       <c r="D146">
-        <v>0.7584690094343834</v>
+        <v>0.6468142267138134</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B147">
         <v>5</v>
       </c>
       <c r="C147">
-        <v>0.9725640746865342</v>
+        <v>1.220708779190034</v>
       </c>
       <c r="D147">
-        <v>0.6042880357003871</v>
+        <v>0.7584690094343834</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B148">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C148">
-        <v>0.6333670840922766</v>
+        <v>0.9725640746865342</v>
       </c>
       <c r="D148">
-        <v>0.4568777756411153</v>
+        <v>0.6042880357003871</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="C149">
-        <v>1.039130927084559</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D149">
-        <v>0.749574517669622</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150">
-        <v>1.021094815861843</v>
+        <v>1.039130927084559</v>
       </c>
       <c r="D150">
-        <v>0.634441880592677</v>
+        <v>0.749574517669622</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B151">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C151">
-        <v>0.2269283709027674</v>
+        <v>1.021094815861843</v>
       </c>
       <c r="D151">
-        <v>0.2065591048302231</v>
+        <v>0.634441880592677</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B152">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>1.095531624518855</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D152">
-        <v>0.5629918858538799</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C153">
-        <v>0.9946503393488847</v>
+        <v>1.095531624518855</v>
       </c>
       <c r="D153">
-        <v>0.618011003509035</v>
+        <v>0.5629918858538799</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B154">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C154">
-        <v>1.237596058536554</v>
+        <v>0.9946503393488847</v>
       </c>
       <c r="D154">
-        <v>0.635998563005272</v>
+        <v>0.618011003509035</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B155">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155">
-        <v>1.237761253347768</v>
+        <v>1.237596058536554</v>
       </c>
       <c r="D155">
-        <v>0.6908077086267796</v>
+        <v>0.635998563005272</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C156">
-        <v>1.121900162570469</v>
+        <v>1.237761253347768</v>
       </c>
       <c r="D156">
-        <v>0.8092799004564688</v>
+        <v>0.6908077086267796</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B157">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C157">
-        <v>1.336219939197759</v>
+        <v>1.121900162570469</v>
       </c>
       <c r="D157">
-        <v>0.7457585474759308</v>
+        <v>0.8092799004564688</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C158">
-        <v>1.314147081896405</v>
+        <v>1.336219939197759</v>
       </c>
       <c r="D158">
-        <v>0.8165254911318077</v>
+        <v>0.7457585474759308</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B159">
         <v>5</v>
       </c>
       <c r="C159">
-        <v>0.9005509293190957</v>
+        <v>1.314147081896405</v>
       </c>
       <c r="D159">
-        <v>0.559543752736078</v>
+        <v>0.8165254911318077</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C160">
-        <v>1.091259044341258</v>
+        <v>0.9005509293190957</v>
       </c>
       <c r="D160">
-        <v>0.7871770057981808</v>
+        <v>0.559543752736078</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C161">
-        <v>0.6931471805599453</v>
+        <v>1.091259044341258</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>0.7871770057981808</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C162">
-        <v>1.107408753153915</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D162">
-        <v>0.7988265582060918</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B163">
         <v>4</v>
       </c>
       <c r="C163">
-        <v>1.21834612096083</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D163">
-        <v>0.8788509533982471</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B164">
         <v>4</v>
       </c>
       <c r="C164">
-        <v>1.173705180235459</v>
+        <v>1.21834612096083</v>
       </c>
       <c r="D164">
-        <v>0.8466493214956918</v>
+        <v>0.8788509533982471</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165">
-        <v>1.107408753153915</v>
+        <v>1.173705180235459</v>
       </c>
       <c r="D165">
-        <v>0.7988265582060918</v>
+        <v>0.8466493214956918</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B166">
         <v>4</v>
       </c>
       <c r="C166">
-        <v>1.321088769299851</v>
+        <v>1.107408753153915</v>
       </c>
       <c r="D166">
-        <v>0.9529641080214998</v>
+        <v>0.7988265582060918</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B167">
         <v>4</v>
       </c>
       <c r="C167">
-        <v>1.301464101246379</v>
+        <v>1.321088769299851</v>
       </c>
       <c r="D167">
-        <v>0.9388079023815816</v>
+        <v>0.9529641080214998</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168">
-        <v>0.5116118989174834</v>
+        <v>1.301464101246379</v>
       </c>
       <c r="D168">
-        <v>0.3178823457338133</v>
+        <v>0.9388079023815816</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B169">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C169">
-        <v>0.673030158126667</v>
+        <v>0.5116118989174834</v>
       </c>
       <c r="D169">
-        <v>0.6126184506297554</v>
+        <v>0.3178823457338133</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C170">
-        <v>1.020592004227205</v>
+        <v>0.673030158126667</v>
       </c>
       <c r="D170">
-        <v>0.7362015116347587</v>
+        <v>0.6126184506297554</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B171">
         <v>4</v>
       </c>
       <c r="C171">
-        <v>1.130808521297513</v>
+        <v>1.020592004227205</v>
       </c>
       <c r="D171">
-        <v>0.8157059229354519</v>
+        <v>0.7362015116347587</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
-        <v>1.123266013178042</v>
+        <v>1.130808521297513</v>
       </c>
       <c r="D172">
-        <v>0.6979244147910146</v>
+        <v>0.8157059229354519</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C173">
-        <v>0.8632649353185766</v>
+        <v>1.123266013178042</v>
       </c>
       <c r="D173">
-        <v>0.6227140205787212</v>
+        <v>0.6979244147910146</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B174">
         <v>4</v>
       </c>
       <c r="C174">
-        <v>0.1895074258256648</v>
+        <v>0.8632649353185766</v>
       </c>
       <c r="D174">
-        <v>0.1367007117251599</v>
+        <v>0.6227140205787212</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B175">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C175">
-        <v>0.846059662603294</v>
+        <v>0.1895074258256648</v>
       </c>
       <c r="D175">
-        <v>0.7701166929681853</v>
+        <v>0.1367007117251599</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B176">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C176">
-        <v>0.997013883990751</v>
+        <v>0.846059662603294</v>
       </c>
       <c r="D176">
-        <v>0.5564440434743706</v>
+        <v>0.7701166929681853</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B177">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C177">
-        <v>0.3732435945336031</v>
+        <v>0.997013883990751</v>
       </c>
       <c r="D177">
-        <v>0.3397409608316878</v>
+        <v>0.5564440434743706</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B178">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C178">
-        <v>1.157836493449356</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D178">
-        <v>0.4659476819976865</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B179">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C179">
-        <v>1.218987605137656</v>
+        <v>1.157836493449356</v>
       </c>
       <c r="D179">
-        <v>0.6803299360615819</v>
+        <v>0.4659476819976865</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C180">
-        <v>1.193289014574816</v>
+        <v>1.218987605137656</v>
       </c>
       <c r="D180">
-        <v>0.7414321517815469</v>
+        <v>0.6803299360615819</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B181">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C181">
-        <v>0.627941588739906</v>
+        <v>1.193289014574816</v>
       </c>
       <c r="D181">
-        <v>0.9059282160429994</v>
+        <v>0.7414321517815469</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B182">
         <v>2</v>
       </c>
       <c r="C182">
-        <v>0.4555869118836413</v>
+        <v>0.627941588739906</v>
       </c>
       <c r="D182">
-        <v>0.6572729784684465</v>
+        <v>0.9059282160429994</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B183">
         <v>2</v>
       </c>
       <c r="C183">
-        <v>0.662192181868297</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D183">
-        <v>0.9553413768968346</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B184">
         <v>2</v>
       </c>
       <c r="C184">
-        <v>0.6931471805599453</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B185">
         <v>2</v>
       </c>
       <c r="C185">
-        <v>0.662192181868297</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D185">
-        <v>0.9553413768968346</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B186">
@@ -3339,7 +3339,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B187">
@@ -3355,7 +3355,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B188">
@@ -3371,103 +3371,103 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>0.607271814155035</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D189">
-        <v>0.5527626264687555</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B190">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C190">
-        <v>0.7389811416400135</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D190">
-        <v>0.459154799281685</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C191">
-        <v>1.113072547203418</v>
+        <v>0.7389811416400135</v>
       </c>
       <c r="D191">
-        <v>0.6212176167166921</v>
+        <v>0.459154799281685</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C192">
-        <v>1.059361955089344</v>
+        <v>1.113072547203418</v>
       </c>
       <c r="D192">
-        <v>0.6582185910403799</v>
+        <v>0.6212176167166921</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C193">
-        <v>0.6729739836656659</v>
+        <v>1.059361955089344</v>
       </c>
       <c r="D193">
-        <v>0.4854481144408732</v>
+        <v>0.6582185910403799</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C194">
-        <v>0.3732435945336031</v>
+        <v>0.6729739836656659</v>
       </c>
       <c r="D194">
-        <v>0.3397409608316878</v>
+        <v>0.4854481144408732</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B195">
@@ -3483,340 +3483,340 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196">
-        <v>0.19451688279324</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D196">
-        <v>0.2806285421749871</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B197">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C197">
-        <v>1.04672998205601</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D197">
-        <v>0.5841911261152554</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B198">
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.9081755830687502</v>
+        <v>1.04672998205601</v>
       </c>
       <c r="D198">
-        <v>0.5068624436850445</v>
+        <v>0.5841911261152554</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B199">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C199">
-        <v>0.862314347241475</v>
+        <v>0.9081755830687502</v>
       </c>
       <c r="D199">
-        <v>0.5357860285130963</v>
+        <v>0.5068624436850445</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B200">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200">
-        <v>1.048179980606054</v>
+        <v>0.862314347241475</v>
       </c>
       <c r="D200">
-        <v>0.5850003857145191</v>
+        <v>0.5357860285130963</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B201">
         <v>6</v>
       </c>
       <c r="C201">
-        <v>1.068652425547084</v>
+        <v>1.048179980606054</v>
       </c>
       <c r="D201">
-        <v>0.5964262747875932</v>
+        <v>0.5850003857145191</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B202">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C202">
-        <v>1.076018254207006</v>
+        <v>1.068652425547084</v>
       </c>
       <c r="D202">
-        <v>0.6685677315626579</v>
+        <v>0.5964262747875932</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C203">
-        <v>0.8866650050430345</v>
+        <v>1.076018254207006</v>
       </c>
       <c r="D203">
-        <v>0.6395936028526868</v>
+        <v>0.6685677315626579</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B204">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C204">
-        <v>1.287673134890783</v>
+        <v>0.8866650050430345</v>
       </c>
       <c r="D204">
-        <v>0.619239881997626</v>
+        <v>0.6395936028526868</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B205">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C205">
-        <v>1.019056018424425</v>
+        <v>1.287673134890783</v>
       </c>
       <c r="D205">
-        <v>0.7350935320844851</v>
+        <v>0.619239881997626</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C206">
-        <v>1.048792231404724</v>
+        <v>1.019056018424425</v>
       </c>
       <c r="D206">
-        <v>0.9546518296060714</v>
+        <v>0.7350935320844851</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B207">
         <v>3</v>
       </c>
       <c r="C207">
-        <v>0.8102359754965719</v>
+        <v>1.048792231404724</v>
       </c>
       <c r="D207">
-        <v>0.7375085677212407</v>
+        <v>0.9546518296060714</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B208">
         <v>3</v>
       </c>
       <c r="C208">
-        <v>0.8036765417474231</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D208">
-        <v>0.7315379138183056</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B209">
         <v>3</v>
       </c>
       <c r="C209">
-        <v>0.9869180017300152</v>
+        <v>0.8036765417474231</v>
       </c>
       <c r="D209">
-        <v>0.8983314786388328</v>
+        <v>0.7315379138183056</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B210">
         <v>3</v>
       </c>
       <c r="C210">
-        <v>0.7410876939721115</v>
+        <v>0.9869180017300152</v>
       </c>
       <c r="D210">
-        <v>0.674567089423841</v>
+        <v>0.8983314786388328</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B211">
         <v>3</v>
       </c>
       <c r="C211">
-        <v>0.6355993030023191</v>
+        <v>0.7410876939721115</v>
       </c>
       <c r="D211">
-        <v>0.5785474180093878</v>
+        <v>0.674567089423841</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B212">
         <v>3</v>
       </c>
       <c r="C212">
-        <v>0.4833021896008116</v>
+        <v>0.6355993030023191</v>
       </c>
       <c r="D212">
-        <v>0.4399206112892998</v>
+        <v>0.5785474180093878</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C213">
-        <v>0.4555869118836413</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D213">
-        <v>0.6572729784684465</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>0.4555869118836413</v>
+      </c>
+      <c r="D214">
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C215">
-        <v>0.8036765417474231</v>
-      </c>
-      <c r="D215">
-        <v>0.7315379138183056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>0.19451688279324</v>
+        <v>0.8036765417474231</v>
       </c>
       <c r="D216">
-        <v>0.2806285421749871</v>
+        <v>0.7315379138183056</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B217">
@@ -3832,263 +3832,263 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B218">
         <v>2</v>
       </c>
       <c r="C218">
-        <v>0.4555869118836413</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D218">
-        <v>0.6572729784684465</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B219">
         <v>2</v>
       </c>
       <c r="C219">
-        <v>0.19451688279324</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D219">
-        <v>0.2806285421749871</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B220">
         <v>2</v>
       </c>
       <c r="C220">
-        <v>0.2449300267946353</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D220">
-        <v>0.3533593350214213</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C221">
-        <v>0.607271814155035</v>
+        <v>0.2449300267946353</v>
       </c>
       <c r="D221">
-        <v>0.5527626264687555</v>
+        <v>0.3533593350214213</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B222">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>1.156027655202271</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D222">
-        <v>0.4652197519375215</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B223">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C223">
-        <v>0.9683146857576469</v>
+        <v>1.156027655202271</v>
       </c>
       <c r="D223">
-        <v>0.3775180523314358</v>
+        <v>0.4652197519375215</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B224">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C224">
-        <v>0.5216705256352127</v>
+        <v>0.9683146857576469</v>
       </c>
       <c r="D224">
-        <v>0.2508704934372867</v>
+        <v>0.3775180523314358</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B225">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C225">
-        <v>0.4034855815444305</v>
+        <v>0.5216705256352127</v>
       </c>
       <c r="D225">
-        <v>0.2910533237821747</v>
+        <v>0.2508704934372867</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B226">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C226">
-        <v>1.213630920484374</v>
+        <v>0.4034855815444305</v>
       </c>
       <c r="D226">
-        <v>0.6236829182855944</v>
+        <v>0.2910533237821747</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B227">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C227">
-        <v>0.5081267731378364</v>
+        <v>1.213630920484374</v>
       </c>
       <c r="D227">
-        <v>0.2044852562896828</v>
+        <v>0.6236829182855944</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B228">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C228">
-        <v>1.184605387662923</v>
+        <v>0.5081267731378364</v>
       </c>
       <c r="D228">
-        <v>0.5391371459621421</v>
+        <v>0.2044852562896828</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B229">
         <v>9</v>
       </c>
       <c r="C229">
-        <v>1.14755889450532</v>
+        <v>1.184605387662923</v>
       </c>
       <c r="D229">
-        <v>0.5222765603216356</v>
+        <v>0.5391371459621421</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C230">
-        <v>1.531798519549437</v>
+        <v>1.14755889450532</v>
       </c>
       <c r="D230">
-        <v>0.7366393759316762</v>
+        <v>0.5222765603216356</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B231">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C231">
-        <v>0.836386862720723</v>
+        <v>1.531798519549437</v>
       </c>
       <c r="D231">
-        <v>0.6033255895559327</v>
+        <v>0.7366393759316762</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B232">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C232">
-        <v>1.068652425547084</v>
+        <v>0.836386862720723</v>
       </c>
       <c r="D232">
-        <v>0.5964262747875932</v>
+        <v>0.6033255895559327</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C233">
-        <v>0.607271814155035</v>
+        <v>1.068652425547084</v>
       </c>
       <c r="D233">
-        <v>0.5527626264687555</v>
+        <v>0.5964262747875932</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B234">
@@ -4104,103 +4104,103 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B235">
         <v>3</v>
       </c>
       <c r="C235">
-        <v>0.8102359754965719</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D235">
-        <v>0.7375085677212407</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C236">
-        <v>0.8170082613435337</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D236">
-        <v>0.5893468835028152</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B237">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C237">
-        <v>0.8102359754965719</v>
+        <v>0.8170082613435337</v>
       </c>
       <c r="D237">
-        <v>0.7375085677212407</v>
+        <v>0.5893468835028152</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B238">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C238">
-        <v>1.430458048303307</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D238">
-        <v>0.6510295138048688</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B239">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C239">
-        <v>1.02998864247627</v>
+        <v>1.430458048303307</v>
       </c>
       <c r="D239">
-        <v>0.9375360653620259</v>
+        <v>0.6510295138048688</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B240">
         <v>3</v>
       </c>
       <c r="C240">
-        <v>0.8699354897077656</v>
+        <v>1.02998864247627</v>
       </c>
       <c r="D240">
-        <v>0.7918494073668355</v>
+        <v>0.9375360653620259</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B241">
@@ -4216,55 +4216,55 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>241</t>
         </is>
       </c>
       <c r="B242">
         <v>3</v>
       </c>
       <c r="C242">
-        <v>0.6900175350139677</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D242">
-        <v>0.6280810274300705</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243">
-        <v>0.6931471805599453</v>
+        <v>0.6900175350139677</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0.6280810274300705</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C244">
-        <v>0.8699354897077656</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D244">
-        <v>0.7918494073668355</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>244</t>
         </is>
       </c>
       <c r="B245">
@@ -4280,7 +4280,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B246">
@@ -4296,39 +4296,39 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C247">
-        <v>0.662192181868297</v>
+        <v>0.8699354897077656</v>
       </c>
       <c r="D247">
-        <v>0.9553413768968346</v>
+        <v>0.7918494073668355</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B248">
         <v>2</v>
       </c>
       <c r="C248">
-        <v>0.4555869118836413</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D248">
-        <v>0.6572729784684465</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B249">
@@ -4344,215 +4344,215 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B250">
         <v>2</v>
       </c>
       <c r="C250">
-        <v>0.19451688279324</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D250">
-        <v>0.2806285421749871</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C251">
-        <v>0.4555869118836413</v>
+        <v>0.3589817088210546</v>
       </c>
       <c r="D251">
-        <v>0.6572729784684465</v>
+        <v>0.3267592330104572</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B252">
         <v>2</v>
       </c>
       <c r="C252">
-        <v>0.4555869118836413</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D252">
-        <v>0.6572729784684465</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C253">
-        <v>0.5380247029595945</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D253">
-        <v>0.3342935436048542</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B254">
         <v>2</v>
       </c>
       <c r="C254">
-        <v>0.19451688279324</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D254">
-        <v>0.2806285421749871</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B255">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C255">
-        <v>0.20276290568803</v>
+        <v>0.5380247029595945</v>
       </c>
       <c r="D255">
-        <v>0.1845627504620828</v>
+        <v>0.3342935436048542</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B256">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C256">
-        <v>0.2351010815977794</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D256">
-        <v>0.169589582264374</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B257">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C257">
-        <v>0.4555869118836413</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D257">
-        <v>0.6572729784684465</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B258">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C258">
-        <v>0.4833021896008116</v>
+        <v>0.2351010815977794</v>
       </c>
       <c r="D258">
-        <v>0.4399206112892998</v>
+        <v>0.169589582264374</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B259">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C259">
-        <v>0.4833021896008116</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D259">
-        <v>0.4399206112892998</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B260">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C260">
-        <v>0.4555869118836413</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D260">
-        <v>0.6572729784684465</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C261">
-        <v>0.662192181868297</v>
+        <v>0.4833021896008116</v>
       </c>
       <c r="D261">
-        <v>0.9553413768968346</v>
+        <v>0.4399206112892998</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B262">
         <v>2</v>
       </c>
       <c r="C262">
-        <v>0.6931471805599453</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B263">
@@ -4568,7 +4568,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B264">
@@ -4584,7 +4584,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>264</t>
         </is>
       </c>
       <c r="B265">
@@ -4600,247 +4600,247 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>265</t>
         </is>
       </c>
       <c r="B266">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C266">
-        <v>0.4626659965444074</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D266">
-        <v>0.4211367388811164</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>266</t>
         </is>
       </c>
       <c r="B267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C267">
-        <v>0.20276290568803</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D267">
-        <v>0.1845627504620828</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B268">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C268">
-        <v>0.2590219627222835</v>
+        <v>0.4626659965444074</v>
       </c>
       <c r="D268">
-        <v>0.1868448505503822</v>
+        <v>0.4211367388811164</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B269">
         <v>3</v>
       </c>
       <c r="C269">
-        <v>0.607271814155035</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D269">
-        <v>0.5527626264687555</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C270">
-        <v>0.8102359754965719</v>
+        <v>0.2590219627222835</v>
       </c>
       <c r="D270">
-        <v>0.7375085677212407</v>
+        <v>0.1868448505503822</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>270</t>
         </is>
       </c>
       <c r="B271">
         <v>3</v>
       </c>
       <c r="C271">
-        <v>1.048792231404724</v>
+        <v>0.607271814155035</v>
       </c>
       <c r="D271">
-        <v>0.9546518296060714</v>
+        <v>0.5527626264687555</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C272">
-        <v>0.19451688279324</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D272">
-        <v>0.2806285421749871</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C273">
-        <v>0.662192181868297</v>
+        <v>1.048792231404724</v>
       </c>
       <c r="D273">
-        <v>0.9553413768968346</v>
+        <v>0.9546518296060714</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C274">
-        <v>0.8102359754965719</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D274">
-        <v>0.7375085677212407</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B275">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C275">
-        <v>0.5638225808048839</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D275">
-        <v>0.513213429906585</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B276">
         <v>3</v>
       </c>
       <c r="C276">
-        <v>0.2269283709027674</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D276">
-        <v>0.2065591048302231</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C277">
-        <v>0.5975603177003802</v>
+        <v>0.5638225808048839</v>
       </c>
       <c r="D277">
-        <v>0.431048653489186</v>
+        <v>0.513213429906585</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C278">
-        <v>0.662192181868297</v>
+        <v>0.2269283709027674</v>
       </c>
       <c r="D278">
-        <v>0.9553413768968346</v>
+        <v>0.2065591048302231</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B279">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C279">
-        <v>0.6931471805599453</v>
+        <v>0.5975603177003802</v>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>0.431048653489186</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C280">
-        <v>0.7280100277746424</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D280">
-        <v>0.6626632846581728</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B281">
@@ -4856,583 +4856,583 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C282">
-        <v>0.662192181868297</v>
+        <v>0.7280100277746424</v>
       </c>
       <c r="D282">
-        <v>0.9553413768968346</v>
+        <v>0.6626632846581728</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B283">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C283">
-        <v>1.365304352400869</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D283">
-        <v>0.7619908675515937</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B284">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C284">
-        <v>1.218987605137656</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D284">
-        <v>0.6803299360615819</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B285">
         <v>6</v>
       </c>
       <c r="C285">
-        <v>1.245446142364597</v>
+        <v>1.365304352400869</v>
       </c>
       <c r="D285">
-        <v>0.695096726850939</v>
+        <v>0.7619908675515937</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>285</t>
         </is>
       </c>
       <c r="B286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C286">
-        <v>1.213579666667576</v>
+        <v>1.218987605137656</v>
       </c>
       <c r="D286">
-        <v>0.7540394427717741</v>
+        <v>0.6803299360615819</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B287">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C287">
-        <v>1.228890586157654</v>
+        <v>1.245446142364597</v>
       </c>
       <c r="D287">
-        <v>0.763552651931189</v>
+        <v>0.695096726850939</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B288">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C288">
-        <v>1.715612302311079</v>
+        <v>1.213579666667576</v>
       </c>
       <c r="D288">
-        <v>0.6688679046704358</v>
+        <v>0.7540394427717741</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B289">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C289">
-        <v>1.096342189139819</v>
+        <v>1.228890586157654</v>
       </c>
       <c r="D289">
-        <v>0.4761353630211544</v>
+        <v>0.763552651931189</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B290">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C290">
-        <v>1.515376040227951</v>
+        <v>1.715612302311079</v>
       </c>
       <c r="D290">
-        <v>0.6581194522793991</v>
+        <v>0.6688679046704358</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B291">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C291">
-        <v>0.19451688279324</v>
+        <v>1.096342189139819</v>
       </c>
       <c r="D291">
-        <v>0.2806285421749871</v>
+        <v>0.4761353630211544</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>291</t>
         </is>
       </c>
       <c r="B292">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C292">
-        <v>1.25279924147191</v>
+        <v>1.515376040227951</v>
       </c>
       <c r="D292">
-        <v>0.7784079347162806</v>
+        <v>0.6581194522793991</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B293">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C293">
-        <v>0.2351010815977794</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D293">
-        <v>0.169589582264374</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="B294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C294">
-        <v>1.039130927084559</v>
+        <v>1.25279924147191</v>
       </c>
       <c r="D294">
-        <v>0.749574517669622</v>
+        <v>0.7784079347162806</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B295">
         <v>4</v>
       </c>
       <c r="C295">
-        <v>0.6333670840922766</v>
+        <v>0.2351010815977794</v>
       </c>
       <c r="D295">
-        <v>0.4568777756411153</v>
+        <v>0.169589582264374</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B296">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C296">
-        <v>0.6693692425153493</v>
+        <v>1.039130927084559</v>
       </c>
       <c r="D296">
-        <v>0.6092861416349635</v>
+        <v>0.749574517669622</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B297">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C297">
-        <v>0.6693692425153493</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D297">
-        <v>0.6092861416349635</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B298">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C298">
-        <v>0.19451688279324</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D298">
-        <v>0.2806285421749871</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>298</t>
         </is>
       </c>
       <c r="B299">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C299">
-        <v>0.7175942382675135</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D299">
-        <v>0.5176348244595175</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C300">
-        <v>0.7022678492315573</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D300">
-        <v>0.6392317439694251</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301">
-        <v>1.038856574934295</v>
+        <v>0.7175942382675135</v>
       </c>
       <c r="D301">
-        <v>0.6454778820036224</v>
+        <v>0.5176348244595175</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B302">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C302">
-        <v>0.6333670840922766</v>
+        <v>0.7022678492315573</v>
       </c>
       <c r="D302">
-        <v>0.4568777756411153</v>
+        <v>0.6392317439694251</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B303">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C303">
-        <v>0.4555869118836413</v>
+        <v>1.038856574934295</v>
       </c>
       <c r="D303">
-        <v>0.6572729784684465</v>
+        <v>0.6454778820036224</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B304">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C304">
-        <v>0.6122032264460429</v>
+        <v>0.6333670840922766</v>
       </c>
       <c r="D304">
-        <v>0.8832225588099292</v>
+        <v>0.4568777756411153</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>304</t>
         </is>
       </c>
       <c r="B305">
         <v>2</v>
       </c>
       <c r="C305">
-        <v>0.6931471805599453</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D305">
-        <v>1</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>305</t>
         </is>
       </c>
       <c r="B306">
         <v>2</v>
       </c>
       <c r="C306">
-        <v>0.662192181868297</v>
+        <v>0.6122032264460429</v>
       </c>
       <c r="D306">
-        <v>0.9553413768968346</v>
+        <v>0.8832225588099292</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B307">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C307">
-        <v>0.3732435945336031</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D307">
-        <v>0.3397409608316878</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B308">
         <v>2</v>
       </c>
       <c r="C308">
-        <v>0.6931471805599453</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B309">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C309">
-        <v>0.662192181868297</v>
+        <v>0.3732435945336031</v>
       </c>
       <c r="D309">
-        <v>0.9553413768968346</v>
+        <v>0.3397409608316878</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B310">
         <v>2</v>
       </c>
       <c r="C310">
-        <v>0.662192181868297</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D310">
-        <v>0.9553413768968346</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C311">
-        <v>0.6900175350139677</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D311">
-        <v>0.6280810274300705</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C312">
-        <v>0.20276290568803</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D312">
-        <v>0.1845627504620828</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B313">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C313">
-        <v>0.5107803845959885</v>
+        <v>0.6900175350139677</v>
       </c>
       <c r="D313">
-        <v>0.3684501639199951</v>
+        <v>0.6280810274300705</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B314">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C314">
-        <v>0.4555869118836413</v>
+        <v>0.20276290568803</v>
       </c>
       <c r="D314">
-        <v>0.6572729784684465</v>
+        <v>0.1845627504620828</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B315">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C315">
-        <v>0.4555869118836413</v>
+        <v>0.5107803845959885</v>
       </c>
       <c r="D315">
-        <v>0.6572729784684465</v>
+        <v>0.3684501639199951</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B316">
         <v>2</v>
       </c>
       <c r="C316">
-        <v>0.662192181868297</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D316">
-        <v>0.9553413768968346</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B317">
         <v>2</v>
       </c>
       <c r="C317">
-        <v>0.6931471805599453</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D317">
-        <v>1</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B318">
@@ -5448,87 +5448,87 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B319">
         <v>2</v>
       </c>
       <c r="C319">
-        <v>0.662192181868297</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D319">
-        <v>0.9553413768968346</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B320">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C320">
-        <v>0.9266767387691077</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D320">
-        <v>0.575776630841018</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B321">
         <v>2</v>
       </c>
       <c r="C321">
-        <v>0.19451688279324</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D321">
-        <v>0.2806285421749871</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B322">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C322">
-        <v>0.662192181868297</v>
+        <v>0.9266767387691077</v>
       </c>
       <c r="D322">
-        <v>0.9553413768968346</v>
+        <v>0.575776630841018</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B323">
         <v>2</v>
       </c>
       <c r="C323">
-        <v>0.662192181868297</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D323">
-        <v>0.9553413768968346</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B324">
@@ -5544,23 +5544,23 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B325">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325">
-        <v>0.6693692425153493</v>
+        <v>0.662192181868297</v>
       </c>
       <c r="D325">
-        <v>0.6092861416349635</v>
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B326">
@@ -5576,23 +5576,23 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B327">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C327">
-        <v>0.755017152900669</v>
+        <v>0.6693692425153493</v>
       </c>
       <c r="D327">
-        <v>0.4213830962623312</v>
+        <v>0.6092861416349635</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B328">
@@ -5608,113 +5608,116 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B329">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C329">
-        <v>0.4555869118836413</v>
+        <v>0.755017152900669</v>
       </c>
       <c r="D329">
-        <v>0.6572729784684465</v>
+        <v>0.4213830962623312</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C330">
-        <v>0</v>
+        <v>0.662192181868297</v>
+      </c>
+      <c r="D330">
+        <v>0.9553413768968346</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B331">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C331">
-        <v>1.09861228866811</v>
+        <v>0.4555869118836413</v>
       </c>
       <c r="D331">
-        <v>0.9999999999999998</v>
+        <v>0.6572729784684465</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B332">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C332">
-        <v>1.121900162570469</v>
-      </c>
-      <c r="D332">
-        <v>0.8092799004564688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C333">
-        <v>0.19451688279324</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D333">
-        <v>0.2806285421749871</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B334">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C334">
-        <v>0.19451688279324</v>
+        <v>1.121900162570469</v>
       </c>
       <c r="D334">
-        <v>0.2806285421749871</v>
+        <v>0.8092799004564688</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C335">
-        <v>0</v>
+        <v>0.19451688279324</v>
+      </c>
+      <c r="D335">
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B336">
@@ -5730,23 +5733,20 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B337">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C337">
-        <v>0.19451688279324</v>
-      </c>
-      <c r="D337">
-        <v>0.2806285421749871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B338">
@@ -5762,7 +5762,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B339">
@@ -5778,7 +5778,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B340">
@@ -5794,144 +5794,176 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B341">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C341">
-        <v>0.8102359754965719</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D341">
-        <v>0.7375085677212407</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B342">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C342">
-        <v>0.9485670767867524</v>
+        <v>0.19451688279324</v>
       </c>
       <c r="D342">
-        <v>0.5294053655513394</v>
+        <v>0.2806285421749871</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B343">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C343">
-        <v>0.4127157986058386</v>
+        <v>0.8102359754965719</v>
       </c>
       <c r="D343">
-        <v>0.2977115179725858</v>
+        <v>0.7375085677212407</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B344">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C344">
-        <v>0.00883143005016138</v>
+        <v>0.9485670767867524</v>
       </c>
       <c r="D344">
-        <v>0.01274106033732559</v>
+        <v>0.5294053655513394</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B345">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C345">
-        <v>1.247010772072043</v>
+        <v>0.4127157986058386</v>
       </c>
       <c r="D345">
-        <v>0.7748113564605138</v>
+        <v>0.2977115179725858</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B346">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C346">
-        <v>0.2771070250309874</v>
+        <v>0.00883143005016138</v>
       </c>
       <c r="D346">
-        <v>0.1721762752636373</v>
+        <v>0.01274106033732559</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B347">
         <v>5</v>
       </c>
       <c r="C347">
-        <v>0.6446717045884102</v>
+        <v>1.247010772072043</v>
       </c>
       <c r="D347">
-        <v>0.4005570513828732</v>
+        <v>0.7748113564605138</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B348">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C348">
-        <v>1.39837008467158</v>
+        <v>0.2771070250309874</v>
       </c>
       <c r="D348">
-        <v>0.7186200685321729</v>
+        <v>0.1721762752636373</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="B349">
+        <v>5</v>
+      </c>
+      <c r="C349">
+        <v>0.6446717045884102</v>
+      </c>
+      <c r="D349">
+        <v>0.4005570513828732</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="B350">
+        <v>7</v>
+      </c>
+      <c r="C350">
+        <v>1.39837008467158</v>
+      </c>
+      <c r="D350">
+        <v>0.7186200685321729</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="B349">
-        <v>3</v>
-      </c>
-      <c r="C349">
+      <c r="B351">
+        <v>3</v>
+      </c>
+      <c r="C351">
         <v>0.20276290568803</v>
       </c>
-      <c r="D349">
+      <c r="D351">
         <v>0.1845627504620828</v>
       </c>
     </row>
